--- a/assets/templates/Mevlana Masjid Prayer Times_KALIP.xlsx
+++ b/assets/templates/Mevlana Masjid Prayer Times_KALIP.xlsx
@@ -5,19 +5,19 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2e59e65f8c74b7e4/Belgeler/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\namaz-vakti\desktop-app\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{EB81F08A-8261-4D89-AC32-25A4FC87B718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{299B339C-0CEE-47BE-8DCD-6D2FB52B86E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D615A5E-B86E-4E6F-AA4B-15280209485C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6840" windowWidth="29040" windowHeight="15720" tabRatio="643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-6840" windowWidth="29040" windowHeight="15720" tabRatio="643" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kasım-24" sheetId="56" r:id="rId1"/>
     <sheet name="Odd" sheetId="53" r:id="rId2"/>
     <sheet name="Even" sheetId="54" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual" calcOnSave="0"/>
+  <calcPr calcId="191029" calcMode="manual" calcCompleted="0" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="34">
   <si>
     <t>Day</t>
   </si>
@@ -714,7 +714,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -855,13 +855,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -943,7 +936,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1054,11 +1047,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1099,255 +1118,288 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="11" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="18" fontId="11" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="18" fontId="11" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="18" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="18" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="18" fontId="10" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1363,9 +1415,6 @@
     <xf numFmtId="18" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="18" fontId="10" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1402,38 +1451,11 @@
     <xf numFmtId="18" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1895,52 +1917,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="76"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="76"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="76"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:8" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="76"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="16" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="12" t="s">
@@ -1958,11 +1980,11 @@
       <c r="G5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="76"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1978,7 +2000,7 @@
       <c r="G6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="76"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
@@ -1987,22 +2009,22 @@
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="17">
         <v>0.2638888888888889</v>
       </c>
-      <c r="D7" s="93" t="s">
+      <c r="D7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="18">
         <v>0.65277777777777779</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="17">
         <v>0.75347222222222221</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="18">
         <v>0.80902777777777779</v>
       </c>
-      <c r="H7" s="92"/>
+      <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
@@ -2011,12 +2033,12 @@
       <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="92"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -2025,22 +2047,22 @@
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="28">
         <v>0.24652777777777779</v>
       </c>
-      <c r="D9" s="77" t="s">
+      <c r="D9" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="28">
         <v>0.61111111111111116</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="28">
         <v>0.70833333333333337</v>
       </c>
-      <c r="G9" s="67">
+      <c r="G9" s="27">
         <v>0.76388888888888884</v>
       </c>
-      <c r="H9" s="92"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
@@ -2049,12 +2071,12 @@
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="92"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -2063,20 +2085,20 @@
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="81">
+      <c r="C11" s="29">
         <v>0.25347222222222221</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="83">
+      <c r="D11" s="23"/>
+      <c r="E11" s="31">
         <v>0.60416666666666663</v>
       </c>
-      <c r="F11" s="82">
+      <c r="F11" s="30">
         <v>0.70486111111111116</v>
       </c>
-      <c r="G11" s="82">
+      <c r="G11" s="30">
         <v>0.76041666666666663</v>
       </c>
-      <c r="H11" s="92"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -2085,12 +2107,12 @@
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="92"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
@@ -2099,18 +2121,18 @@
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="80">
+      <c r="C13" s="25">
         <v>0.25694444444444442</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="57">
+      <c r="D13" s="23"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="26">
         <v>0.70138888888888884</v>
       </c>
-      <c r="G13" s="89">
+      <c r="G13" s="37">
         <v>0.75694444444444442</v>
       </c>
-      <c r="H13" s="92"/>
+      <c r="H13" s="19"/>
     </row>
     <row r="14" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
@@ -2119,12 +2141,12 @@
       <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="92"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
@@ -2133,18 +2155,18 @@
       <c r="B15" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="77">
+      <c r="C15" s="22">
         <v>0.26041666666666669</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="86">
+      <c r="D15" s="23"/>
+      <c r="E15" s="34">
         <v>0.60069444444444442</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="27">
         <v>0.69791666666666663</v>
       </c>
-      <c r="G15" s="90"/>
-      <c r="H15" s="76"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
@@ -2153,12 +2175,12 @@
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="76"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
@@ -2167,16 +2189,16 @@
       <c r="B17" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="40">
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="18">
         <v>0.69444444444444442</v>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="18">
         <v>0.75347222222222221</v>
       </c>
-      <c r="H17" s="76"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
@@ -2185,64 +2207,64 @@
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="76"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
     </row>
     <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="52"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
     </row>
     <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="52"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
     </row>
     <row r="27" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="52"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
     </row>
     <row r="28" spans="1:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="16" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -2260,12 +2282,12 @@
       <c r="G28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
     </row>
     <row r="29" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="53"/>
-      <c r="B29" s="53"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="2" t="s">
         <v>6</v>
       </c>
@@ -2281,458 +2303,458 @@
       <c r="G29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
     </row>
     <row r="30" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="60">
+      <c r="A30" s="41">
         <v>1</v>
       </c>
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="68">
+      <c r="C30" s="42">
         <v>0.2013888888888889</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="61">
+      <c r="E30" s="45">
         <v>0.71875</v>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="17">
         <v>0.86458333333333337</v>
       </c>
-      <c r="G30" s="61">
+      <c r="G30" s="45">
         <v>0.9375</v>
       </c>
-      <c r="H30" s="71"/>
-      <c r="I30" s="72"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="49"/>
     </row>
     <row r="31" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="60"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49"/>
     </row>
     <row r="32" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="60"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
     </row>
     <row r="33" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="60">
+      <c r="A33" s="41">
         <v>5</v>
       </c>
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="69"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
     </row>
     <row r="34" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="60"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="59">
+      <c r="A35" s="50">
         <v>6</v>
       </c>
-      <c r="B35" s="59" t="s">
+      <c r="B35" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="46">
+      <c r="C35" s="43"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="51">
         <v>0.86111111111111116</v>
       </c>
-      <c r="G35" s="73">
+      <c r="G35" s="54">
         <v>0.93402777777777779</v>
       </c>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="59"/>
-      <c r="B36" s="59"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
     </row>
     <row r="37" spans="1:9" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="59"/>
-      <c r="B37" s="59"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
     </row>
     <row r="38" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="59">
+      <c r="A38" s="50">
         <v>10</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="69"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="72"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
     </row>
     <row r="39" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="59"/>
-      <c r="B39" s="59"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
     </row>
     <row r="40" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="59"/>
-      <c r="B40" s="59"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="49"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
+      <c r="A40" s="50"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
     </row>
     <row r="41" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="55">
+      <c r="A41" s="57">
         <v>11</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="58">
         <v>0.20833333333333334</v>
       </c>
-      <c r="D41" s="49"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="54"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="40"/>
     </row>
     <row r="42" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="55"/>
-      <c r="B42" s="55"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="54"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="40"/>
     </row>
     <row r="43" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="55">
+      <c r="A43" s="57">
         <v>15</v>
       </c>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="74"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="54"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="40"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="55"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="54"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="61"/>
+      <c r="I44" s="40"/>
     </row>
     <row r="45" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="56">
+      <c r="A45" s="62">
         <v>16</v>
       </c>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="57">
+      <c r="C45" s="59"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="26">
         <v>0.85763888888888884</v>
       </c>
-      <c r="G45" s="64">
+      <c r="G45" s="63">
         <v>0.92708333333333337</v>
       </c>
-      <c r="H45" s="58"/>
-      <c r="I45" s="54"/>
+      <c r="H45" s="61"/>
+      <c r="I45" s="40"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="54"/>
+      <c r="A46" s="62"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="40"/>
     </row>
     <row r="47" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="56"/>
-      <c r="B47" s="56"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="54"/>
+      <c r="A47" s="62"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="40"/>
     </row>
     <row r="48" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="56">
+      <c r="A48" s="62">
         <v>20</v>
       </c>
-      <c r="B48" s="56" t="s">
+      <c r="B48" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="54"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="40"/>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="56"/>
-      <c r="B49" s="56"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="65"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="54"/>
+      <c r="A49" s="62"/>
+      <c r="B49" s="62"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="40"/>
     </row>
     <row r="50" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="59">
+      <c r="A50" s="50">
         <v>21</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="46">
+      <c r="C50" s="51">
         <v>0.21527777777777779</v>
       </c>
-      <c r="D50" s="49"/>
-      <c r="E50" s="62"/>
-      <c r="F50" s="67">
+      <c r="D50" s="17"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="27">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G50" s="65"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61"/>
     </row>
     <row r="51" spans="1:9" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="59"/>
-      <c r="B51" s="59"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="62"/>
-      <c r="F51" s="67"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
+      <c r="A51" s="50"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="64"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61"/>
     </row>
     <row r="52" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="59"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="62"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
+      <c r="A52" s="50"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61"/>
     </row>
     <row r="53" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="59">
+      <c r="A53" s="50">
         <v>25</v>
       </c>
-      <c r="B53" s="59" t="s">
+      <c r="B53" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="47"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="62"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="61"/>
     </row>
     <row r="54" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="59"/>
-      <c r="B54" s="59"/>
-      <c r="C54" s="47"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="62"/>
-      <c r="F54" s="67"/>
-      <c r="G54" s="66"/>
-      <c r="H54" s="58"/>
-      <c r="I54" s="58"/>
+      <c r="A54" s="50"/>
+      <c r="B54" s="50"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="61"/>
+      <c r="I54" s="61"/>
     </row>
     <row r="55" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="60">
+      <c r="A55" s="41">
         <v>26</v>
       </c>
-      <c r="B55" s="60" t="s">
+      <c r="B55" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="47"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="62"/>
-      <c r="F55" s="40">
+      <c r="C55" s="52"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="18">
         <v>0.85069444444444442</v>
       </c>
-      <c r="G55" s="61">
+      <c r="G55" s="45">
         <v>0.92361111111111116</v>
       </c>
-      <c r="H55" s="58"/>
-      <c r="I55" s="58"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
     </row>
     <row r="56" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="60"/>
-      <c r="B56" s="60"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="62"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="58"/>
+      <c r="A56" s="41"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="61"/>
     </row>
     <row r="57" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="60"/>
-      <c r="B57" s="60"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="62"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="62"/>
-      <c r="H57" s="58"/>
-      <c r="I57" s="58"/>
+      <c r="A57" s="41"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61"/>
     </row>
     <row r="58" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="60">
+      <c r="A58" s="41">
         <v>31</v>
       </c>
-      <c r="B58" s="60" t="s">
+      <c r="B58" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="47"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="62"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="62"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="58"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61"/>
     </row>
     <row r="59" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="60"/>
-      <c r="B59" s="60"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="63"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="63"/>
-      <c r="H59" s="58"/>
-      <c r="I59" s="58"/>
+      <c r="A59" s="41"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="47"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61"/>
     </row>
     <row r="65" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="52" t="s">
+      <c r="A65" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B65" s="52"/>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="52"/>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
     </row>
     <row r="67" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="52"/>
-      <c r="B67" s="52"/>
-      <c r="C67" s="52"/>
-      <c r="D67" s="52"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="52"/>
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
     </row>
     <row r="68" spans="1:7" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="52"/>
-      <c r="B68" s="52"/>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="52"/>
+      <c r="A68" s="14"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
     </row>
     <row r="69" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="53" t="s">
+      <c r="A69" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B69" s="53" t="s">
+      <c r="B69" s="16" t="s">
         <v>0</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -2752,8 +2774,8 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="53"/>
-      <c r="B70" s="53"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
       <c r="C70" s="2" t="s">
         <v>6</v>
       </c>
@@ -2771,398 +2793,398 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="34">
+      <c r="A71" s="66">
         <v>1</v>
       </c>
-      <c r="B71" s="34" t="s">
+      <c r="B71" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="49">
+      <c r="C71" s="17">
         <v>0.28472222222222221</v>
       </c>
-      <c r="D71" s="40">
+      <c r="D71" s="18">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E71" s="40">
+      <c r="E71" s="18">
         <v>0.65625</v>
       </c>
-      <c r="F71" s="40">
+      <c r="F71" s="18">
         <v>0.75347222222222221</v>
       </c>
-      <c r="G71" s="40">
+      <c r="G71" s="18">
         <v>0.8125</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="35"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="49"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="40"/>
+      <c r="A72" s="67"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
     </row>
     <row r="73" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="34">
+      <c r="A73" s="66">
         <v>5</v>
       </c>
-      <c r="B73" s="34" t="s">
+      <c r="B73" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="49"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
     </row>
     <row r="74" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="39"/>
-      <c r="B74" s="39"/>
-      <c r="C74" s="49"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
-      <c r="G74" s="40"/>
+      <c r="A74" s="68"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
     </row>
     <row r="75" spans="1:7" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="40"/>
-      <c r="F75" s="40"/>
-      <c r="G75" s="40"/>
+      <c r="A75" s="67"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
     </row>
     <row r="76" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="24">
+      <c r="A76" s="72">
         <v>6</v>
       </c>
-      <c r="B76" s="24" t="s">
+      <c r="B76" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="42">
+      <c r="C76" s="28">
         <v>0.25</v>
       </c>
-      <c r="D76" s="43">
+      <c r="D76" s="69">
         <v>0.5</v>
       </c>
-      <c r="E76" s="42">
+      <c r="E76" s="28">
         <v>0.61458333333333337</v>
       </c>
-      <c r="F76" s="46">
+      <c r="F76" s="51">
         <v>0.70833333333333337</v>
       </c>
-      <c r="G76" s="43">
+      <c r="G76" s="69">
         <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="41"/>
-      <c r="B77" s="41"/>
-      <c r="C77" s="42"/>
-      <c r="D77" s="44"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="47"/>
-      <c r="G77" s="44"/>
+      <c r="A77" s="82"/>
+      <c r="B77" s="82"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="70"/>
     </row>
     <row r="78" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="25"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="42"/>
-      <c r="D78" s="44"/>
-      <c r="E78" s="42"/>
-      <c r="F78" s="47"/>
-      <c r="G78" s="44"/>
+      <c r="A78" s="73"/>
+      <c r="B78" s="73"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="70"/>
     </row>
     <row r="79" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="24">
+      <c r="A79" s="72">
         <v>10</v>
       </c>
-      <c r="B79" s="24" t="s">
+      <c r="B79" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C79" s="42"/>
-      <c r="D79" s="44"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="47"/>
-      <c r="G79" s="44"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="70"/>
     </row>
     <row r="80" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="25"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="42"/>
-      <c r="D80" s="44"/>
-      <c r="E80" s="42"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="44"/>
+      <c r="A80" s="73"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="70"/>
     </row>
     <row r="81" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="34">
+      <c r="A81" s="66">
         <v>11</v>
       </c>
-      <c r="B81" s="34" t="s">
+      <c r="B81" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="C81" s="42"/>
-      <c r="D81" s="44"/>
-      <c r="E81" s="42"/>
-      <c r="F81" s="36">
+      <c r="C81" s="28"/>
+      <c r="D81" s="70"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="74">
         <v>0.70486111111111116</v>
       </c>
-      <c r="G81" s="44"/>
+      <c r="G81" s="70"/>
     </row>
     <row r="82" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="35"/>
-      <c r="B82" s="35"/>
-      <c r="C82" s="42"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="44"/>
+      <c r="A82" s="67"/>
+      <c r="B82" s="67"/>
+      <c r="C82" s="28"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="28"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="70"/>
     </row>
     <row r="83" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="34">
+      <c r="A83" s="66">
         <v>15</v>
       </c>
-      <c r="B83" s="34" t="s">
+      <c r="B83" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="42"/>
-      <c r="D83" s="44"/>
-      <c r="E83" s="42"/>
-      <c r="F83" s="37"/>
-      <c r="G83" s="44"/>
+      <c r="C83" s="28"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="28"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="70"/>
     </row>
     <row r="84" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="39"/>
-      <c r="B84" s="39"/>
-      <c r="C84" s="42"/>
-      <c r="D84" s="44"/>
-      <c r="E84" s="42"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="44"/>
+      <c r="A84" s="68"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="75"/>
+      <c r="G84" s="70"/>
     </row>
     <row r="85" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="35"/>
-      <c r="B85" s="35"/>
-      <c r="C85" s="42"/>
-      <c r="D85" s="44"/>
-      <c r="E85" s="42"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="44"/>
+      <c r="A85" s="67"/>
+      <c r="B85" s="67"/>
+      <c r="C85" s="28"/>
+      <c r="D85" s="70"/>
+      <c r="E85" s="28"/>
+      <c r="F85" s="76"/>
+      <c r="G85" s="70"/>
     </row>
     <row r="86" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="16">
+      <c r="A86" s="79">
         <v>16</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="58">
         <v>0.25694444444444448</v>
       </c>
-      <c r="D86" s="44"/>
-      <c r="E86" s="31">
+      <c r="D86" s="70"/>
+      <c r="E86" s="83">
         <v>0.60416666666666663</v>
       </c>
-      <c r="F86" s="27">
+      <c r="F86" s="77">
         <v>0.70138888888888884</v>
       </c>
-      <c r="G86" s="44"/>
+      <c r="G86" s="70"/>
     </row>
     <row r="87" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="18"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="44"/>
+      <c r="A87" s="81"/>
+      <c r="B87" s="81"/>
+      <c r="C87" s="59"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="84"/>
+      <c r="F87" s="78"/>
+      <c r="G87" s="70"/>
     </row>
     <row r="88" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="16">
+      <c r="A88" s="79">
         <v>20</v>
       </c>
-      <c r="B88" s="19" t="s">
+      <c r="B88" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="C88" s="29"/>
-      <c r="D88" s="44"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="44"/>
+      <c r="C88" s="59"/>
+      <c r="D88" s="70"/>
+      <c r="E88" s="84"/>
+      <c r="F88" s="78"/>
+      <c r="G88" s="70"/>
     </row>
     <row r="89" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="44"/>
-      <c r="E89" s="32"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="44"/>
+      <c r="A89" s="80"/>
+      <c r="B89" s="87"/>
+      <c r="C89" s="59"/>
+      <c r="D89" s="70"/>
+      <c r="E89" s="84"/>
+      <c r="F89" s="78"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="18"/>
-      <c r="B90" s="21"/>
-      <c r="C90" s="29"/>
-      <c r="D90" s="44"/>
-      <c r="E90" s="32"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="44"/>
+      <c r="A90" s="81"/>
+      <c r="B90" s="88"/>
+      <c r="C90" s="59"/>
+      <c r="D90" s="70"/>
+      <c r="E90" s="84"/>
+      <c r="F90" s="78"/>
+      <c r="G90" s="70"/>
     </row>
     <row r="91" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="22">
+      <c r="A91" s="89">
         <v>21</v>
       </c>
-      <c r="B91" s="22" t="s">
+      <c r="B91" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="C91" s="29"/>
-      <c r="D91" s="44"/>
-      <c r="E91" s="32"/>
-      <c r="F91" s="50">
+      <c r="C91" s="59"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="84"/>
+      <c r="F91" s="91">
         <v>0.69791666666666663</v>
       </c>
-      <c r="G91" s="44"/>
+      <c r="G91" s="70"/>
     </row>
     <row r="92" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="23"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="29"/>
-      <c r="D92" s="44"/>
-      <c r="E92" s="32"/>
-      <c r="F92" s="51"/>
-      <c r="G92" s="44"/>
+      <c r="A92" s="90"/>
+      <c r="B92" s="90"/>
+      <c r="C92" s="59"/>
+      <c r="D92" s="70"/>
+      <c r="E92" s="84"/>
+      <c r="F92" s="92"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="22">
+      <c r="A93" s="89">
         <v>25</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C93" s="29"/>
-      <c r="D93" s="44"/>
-      <c r="E93" s="32"/>
-      <c r="F93" s="51"/>
-      <c r="G93" s="44"/>
+      <c r="C93" s="59"/>
+      <c r="D93" s="70"/>
+      <c r="E93" s="84"/>
+      <c r="F93" s="92"/>
+      <c r="G93" s="70"/>
     </row>
     <row r="94" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="26"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="44"/>
-      <c r="E94" s="32"/>
-      <c r="F94" s="51"/>
-      <c r="G94" s="44"/>
+      <c r="A94" s="93"/>
+      <c r="B94" s="93"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="70"/>
+      <c r="E94" s="84"/>
+      <c r="F94" s="92"/>
+      <c r="G94" s="70"/>
     </row>
     <row r="95" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="23"/>
-      <c r="B95" s="23"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="44"/>
-      <c r="E95" s="32"/>
-      <c r="F95" s="51"/>
-      <c r="G95" s="44"/>
+      <c r="A95" s="90"/>
+      <c r="B95" s="90"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="70"/>
+      <c r="E95" s="84"/>
+      <c r="F95" s="92"/>
+      <c r="G95" s="70"/>
     </row>
     <row r="96" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="16">
+      <c r="A96" s="79">
         <v>26</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B96" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="C96" s="29"/>
-      <c r="D96" s="44"/>
-      <c r="E96" s="32"/>
-      <c r="F96" s="27">
+      <c r="C96" s="59"/>
+      <c r="D96" s="70"/>
+      <c r="E96" s="84"/>
+      <c r="F96" s="77">
         <v>0.69444444444444453</v>
       </c>
-      <c r="G96" s="44"/>
+      <c r="G96" s="70"/>
     </row>
     <row r="97" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="18"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="44"/>
-      <c r="E97" s="32"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="44"/>
+      <c r="A97" s="81"/>
+      <c r="B97" s="81"/>
+      <c r="C97" s="59"/>
+      <c r="D97" s="70"/>
+      <c r="E97" s="84"/>
+      <c r="F97" s="78"/>
+      <c r="G97" s="70"/>
     </row>
     <row r="98" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="16">
+      <c r="A98" s="79">
         <v>30</v>
       </c>
-      <c r="B98" s="16" t="s">
+      <c r="B98" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C98" s="29"/>
-      <c r="D98" s="44"/>
-      <c r="E98" s="32"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="44"/>
+      <c r="C98" s="59"/>
+      <c r="D98" s="70"/>
+      <c r="E98" s="84"/>
+      <c r="F98" s="78"/>
+      <c r="G98" s="70"/>
     </row>
     <row r="99" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="17"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="44"/>
-      <c r="E99" s="32"/>
-      <c r="F99" s="14"/>
-      <c r="G99" s="44"/>
+      <c r="A99" s="80"/>
+      <c r="B99" s="80"/>
+      <c r="C99" s="59"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="84"/>
+      <c r="F99" s="78"/>
+      <c r="G99" s="70"/>
     </row>
     <row r="100" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="18"/>
-      <c r="B100" s="18"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="33"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="45"/>
+      <c r="A100" s="81"/>
+      <c r="B100" s="81"/>
+      <c r="C100" s="60"/>
+      <c r="D100" s="71"/>
+      <c r="E100" s="85"/>
+      <c r="F100" s="78"/>
+      <c r="G100" s="71"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="52" t="s">
+      <c r="A104" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B104" s="52"/>
-      <c r="C104" s="52"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="52"/>
-      <c r="B105" s="52"/>
-      <c r="C105" s="52"/>
-      <c r="D105" s="52"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52"/>
-      <c r="G105" s="52"/>
+      <c r="A105" s="14"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
     </row>
     <row r="106" spans="1:7" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="52"/>
-      <c r="B106" s="52"/>
-      <c r="C106" s="52"/>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
+      <c r="A106" s="14"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
     </row>
     <row r="107" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="52"/>
-      <c r="B107" s="52"/>
-      <c r="C107" s="52"/>
-      <c r="D107" s="52"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52"/>
-      <c r="G107" s="52"/>
+      <c r="A107" s="14"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
     </row>
     <row r="108" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A108" s="53" t="s">
+      <c r="A108" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B108" s="53" t="s">
+      <c r="B108" s="16" t="s">
         <v>0</v>
       </c>
       <c r="C108" s="1" t="s">
@@ -3182,8 +3204,8 @@
       </c>
     </row>
     <row r="109" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="53"/>
-      <c r="B109" s="53"/>
+      <c r="A109" s="16"/>
+      <c r="B109" s="16"/>
       <c r="C109" s="2" t="s">
         <v>6</v>
       </c>
@@ -3201,387 +3223,468 @@
       </c>
     </row>
     <row r="110" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="34">
+      <c r="A110" s="66">
         <v>1</v>
       </c>
-      <c r="B110" s="34" t="s">
+      <c r="B110" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="C110" s="49">
+      <c r="C110" s="17">
         <v>0.27083333333333331</v>
       </c>
-      <c r="D110" s="40">
+      <c r="D110" s="18">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E110" s="40">
+      <c r="E110" s="18">
         <v>0.65625</v>
       </c>
-      <c r="F110" s="40">
+      <c r="F110" s="18">
         <v>0.75347222222222221</v>
       </c>
-      <c r="G110" s="40">
+      <c r="G110" s="18">
         <v>0.8125</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="35"/>
-      <c r="B111" s="35"/>
-      <c r="C111" s="49"/>
-      <c r="D111" s="40"/>
-      <c r="E111" s="40"/>
-      <c r="F111" s="40"/>
-      <c r="G111" s="40"/>
+      <c r="A111" s="67"/>
+      <c r="B111" s="67"/>
+      <c r="C111" s="17"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
     </row>
     <row r="112" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="34">
+      <c r="A112" s="66">
         <v>5</v>
       </c>
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C112" s="49"/>
-      <c r="D112" s="40"/>
-      <c r="E112" s="40"/>
-      <c r="F112" s="40"/>
-      <c r="G112" s="40"/>
+      <c r="C112" s="17"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
     </row>
     <row r="113" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="39"/>
-      <c r="B113" s="39"/>
-      <c r="C113" s="49"/>
-      <c r="D113" s="40"/>
-      <c r="E113" s="40"/>
-      <c r="F113" s="40"/>
-      <c r="G113" s="40"/>
+      <c r="A113" s="68"/>
+      <c r="B113" s="68"/>
+      <c r="C113" s="17"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
     </row>
     <row r="114" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="35"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="49"/>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
-      <c r="F114" s="40"/>
-      <c r="G114" s="40"/>
+      <c r="A114" s="67"/>
+      <c r="B114" s="67"/>
+      <c r="C114" s="17"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
     </row>
     <row r="115" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24">
+      <c r="A115" s="72">
         <v>6</v>
       </c>
-      <c r="B115" s="24" t="s">
+      <c r="B115" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="C115" s="42">
+      <c r="C115" s="28">
         <v>0.25</v>
       </c>
-      <c r="D115" s="43">
+      <c r="D115" s="69">
         <v>0.5</v>
       </c>
-      <c r="E115" s="42">
+      <c r="E115" s="28">
         <v>0.61458333333333337</v>
       </c>
-      <c r="F115" s="46">
+      <c r="F115" s="51">
         <v>0.70833333333333337</v>
       </c>
-      <c r="G115" s="46">
+      <c r="G115" s="51">
         <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="41"/>
-      <c r="B116" s="41"/>
-      <c r="C116" s="42"/>
-      <c r="D116" s="44"/>
-      <c r="E116" s="42"/>
-      <c r="F116" s="47"/>
-      <c r="G116" s="47"/>
+      <c r="A116" s="82"/>
+      <c r="B116" s="82"/>
+      <c r="C116" s="28"/>
+      <c r="D116" s="70"/>
+      <c r="E116" s="28"/>
+      <c r="F116" s="52"/>
+      <c r="G116" s="52"/>
     </row>
     <row r="117" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="25"/>
-      <c r="B117" s="25"/>
-      <c r="C117" s="42"/>
-      <c r="D117" s="44"/>
-      <c r="E117" s="42"/>
-      <c r="F117" s="47"/>
-      <c r="G117" s="47"/>
+      <c r="A117" s="73"/>
+      <c r="B117" s="73"/>
+      <c r="C117" s="28"/>
+      <c r="D117" s="70"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="52"/>
+      <c r="G117" s="52"/>
     </row>
     <row r="118" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="24">
+      <c r="A118" s="72">
         <v>10</v>
       </c>
-      <c r="B118" s="24" t="s">
+      <c r="B118" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="42"/>
-      <c r="D118" s="44"/>
-      <c r="E118" s="42"/>
-      <c r="F118" s="47"/>
-      <c r="G118" s="47"/>
+      <c r="C118" s="28"/>
+      <c r="D118" s="70"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="52"/>
+      <c r="G118" s="52"/>
     </row>
     <row r="119" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="25"/>
-      <c r="B119" s="25"/>
-      <c r="C119" s="42"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="42"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="47"/>
+      <c r="A119" s="73"/>
+      <c r="B119" s="73"/>
+      <c r="C119" s="28"/>
+      <c r="D119" s="70"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="53"/>
+      <c r="G119" s="52"/>
     </row>
     <row r="120" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="34">
+      <c r="A120" s="66">
         <v>11</v>
       </c>
-      <c r="B120" s="34" t="s">
+      <c r="B120" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="C120" s="42"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="42"/>
-      <c r="F120" s="36">
+      <c r="C120" s="28"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="28"/>
+      <c r="F120" s="74">
         <v>0.70486111111111116</v>
       </c>
-      <c r="G120" s="47"/>
+      <c r="G120" s="52"/>
     </row>
     <row r="121" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="35"/>
-      <c r="B121" s="35"/>
-      <c r="C121" s="42"/>
-      <c r="D121" s="44"/>
-      <c r="E121" s="42"/>
-      <c r="F121" s="37"/>
-      <c r="G121" s="47"/>
+      <c r="A121" s="67"/>
+      <c r="B121" s="67"/>
+      <c r="C121" s="28"/>
+      <c r="D121" s="70"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="75"/>
+      <c r="G121" s="52"/>
     </row>
     <row r="122" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="34">
+      <c r="A122" s="66">
         <v>15</v>
       </c>
-      <c r="B122" s="34" t="s">
+      <c r="B122" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="C122" s="42"/>
-      <c r="D122" s="44"/>
-      <c r="E122" s="42"/>
-      <c r="F122" s="37"/>
-      <c r="G122" s="47"/>
+      <c r="C122" s="28"/>
+      <c r="D122" s="70"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="75"/>
+      <c r="G122" s="52"/>
     </row>
     <row r="123" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="39"/>
-      <c r="B123" s="39"/>
-      <c r="C123" s="42"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="42"/>
-      <c r="F123" s="37"/>
-      <c r="G123" s="47"/>
+      <c r="A123" s="68"/>
+      <c r="B123" s="68"/>
+      <c r="C123" s="28"/>
+      <c r="D123" s="70"/>
+      <c r="E123" s="28"/>
+      <c r="F123" s="75"/>
+      <c r="G123" s="52"/>
     </row>
     <row r="124" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="35"/>
-      <c r="B124" s="35"/>
-      <c r="C124" s="42"/>
-      <c r="D124" s="44"/>
-      <c r="E124" s="42"/>
-      <c r="F124" s="38"/>
-      <c r="G124" s="47"/>
+      <c r="A124" s="67"/>
+      <c r="B124" s="67"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="70"/>
+      <c r="E124" s="28"/>
+      <c r="F124" s="76"/>
+      <c r="G124" s="52"/>
     </row>
     <row r="125" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="16">
+      <c r="A125" s="79">
         <v>16</v>
       </c>
-      <c r="B125" s="16" t="s">
+      <c r="B125" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C125" s="28">
+      <c r="C125" s="58">
         <v>0.25694444444444448</v>
       </c>
-      <c r="D125" s="44"/>
-      <c r="E125" s="31">
+      <c r="D125" s="70"/>
+      <c r="E125" s="83">
         <v>0.60416666666666663</v>
       </c>
-      <c r="F125" s="27">
+      <c r="F125" s="77">
         <v>0.70138888888888884</v>
       </c>
-      <c r="G125" s="14">
+      <c r="G125" s="78">
         <v>0.76388888888888884</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="18"/>
-      <c r="B126" s="18"/>
-      <c r="C126" s="29"/>
-      <c r="D126" s="44"/>
-      <c r="E126" s="32"/>
-      <c r="F126" s="14"/>
-      <c r="G126" s="14"/>
+      <c r="A126" s="81"/>
+      <c r="B126" s="81"/>
+      <c r="C126" s="59"/>
+      <c r="D126" s="70"/>
+      <c r="E126" s="84"/>
+      <c r="F126" s="78"/>
+      <c r="G126" s="78"/>
     </row>
     <row r="127" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="16">
+      <c r="A127" s="79">
         <v>20</v>
       </c>
-      <c r="B127" s="19" t="s">
+      <c r="B127" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="29"/>
-      <c r="D127" s="44"/>
-      <c r="E127" s="32"/>
-      <c r="F127" s="14"/>
-      <c r="G127" s="14"/>
+      <c r="C127" s="59"/>
+      <c r="D127" s="70"/>
+      <c r="E127" s="84"/>
+      <c r="F127" s="78"/>
+      <c r="G127" s="78"/>
     </row>
     <row r="128" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="17"/>
-      <c r="B128" s="20"/>
-      <c r="C128" s="29"/>
-      <c r="D128" s="44"/>
-      <c r="E128" s="32"/>
-      <c r="F128" s="14"/>
-      <c r="G128" s="14"/>
+      <c r="A128" s="80"/>
+      <c r="B128" s="87"/>
+      <c r="C128" s="59"/>
+      <c r="D128" s="70"/>
+      <c r="E128" s="84"/>
+      <c r="F128" s="78"/>
+      <c r="G128" s="78"/>
     </row>
     <row r="129" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="18"/>
-      <c r="B129" s="21"/>
-      <c r="C129" s="29"/>
-      <c r="D129" s="44"/>
-      <c r="E129" s="32"/>
-      <c r="F129" s="14"/>
-      <c r="G129" s="14"/>
+      <c r="A129" s="81"/>
+      <c r="B129" s="88"/>
+      <c r="C129" s="59"/>
+      <c r="D129" s="70"/>
+      <c r="E129" s="84"/>
+      <c r="F129" s="78"/>
+      <c r="G129" s="78"/>
     </row>
     <row r="130" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="22">
+      <c r="A130" s="89">
         <v>21</v>
       </c>
-      <c r="B130" s="22" t="s">
+      <c r="B130" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="C130" s="29"/>
-      <c r="D130" s="44"/>
-      <c r="E130" s="32"/>
-      <c r="F130" s="50">
+      <c r="C130" s="59"/>
+      <c r="D130" s="70"/>
+      <c r="E130" s="84"/>
+      <c r="F130" s="91">
         <v>0.69791666666666663</v>
       </c>
-      <c r="G130" s="14"/>
+      <c r="G130" s="78"/>
     </row>
     <row r="131" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="23"/>
-      <c r="B131" s="23"/>
-      <c r="C131" s="29"/>
-      <c r="D131" s="44"/>
-      <c r="E131" s="32"/>
-      <c r="F131" s="51"/>
-      <c r="G131" s="14"/>
+      <c r="A131" s="90"/>
+      <c r="B131" s="90"/>
+      <c r="C131" s="59"/>
+      <c r="D131" s="70"/>
+      <c r="E131" s="84"/>
+      <c r="F131" s="92"/>
+      <c r="G131" s="78"/>
     </row>
     <row r="132" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="22">
+      <c r="A132" s="89">
         <v>25</v>
       </c>
-      <c r="B132" s="22" t="s">
+      <c r="B132" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C132" s="29"/>
-      <c r="D132" s="44"/>
-      <c r="E132" s="32"/>
-      <c r="F132" s="51"/>
-      <c r="G132" s="14"/>
+      <c r="C132" s="59"/>
+      <c r="D132" s="70"/>
+      <c r="E132" s="84"/>
+      <c r="F132" s="92"/>
+      <c r="G132" s="78"/>
     </row>
     <row r="133" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="26"/>
-      <c r="B133" s="26"/>
-      <c r="C133" s="29"/>
-      <c r="D133" s="44"/>
-      <c r="E133" s="32"/>
-      <c r="F133" s="51"/>
-      <c r="G133" s="14"/>
+      <c r="A133" s="93"/>
+      <c r="B133" s="93"/>
+      <c r="C133" s="59"/>
+      <c r="D133" s="70"/>
+      <c r="E133" s="84"/>
+      <c r="F133" s="92"/>
+      <c r="G133" s="78"/>
     </row>
     <row r="134" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="23"/>
-      <c r="B134" s="23"/>
-      <c r="C134" s="29"/>
-      <c r="D134" s="44"/>
-      <c r="E134" s="32"/>
-      <c r="F134" s="51"/>
-      <c r="G134" s="14"/>
+      <c r="A134" s="90"/>
+      <c r="B134" s="90"/>
+      <c r="C134" s="59"/>
+      <c r="D134" s="70"/>
+      <c r="E134" s="84"/>
+      <c r="F134" s="92"/>
+      <c r="G134" s="78"/>
     </row>
     <row r="135" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="16">
+      <c r="A135" s="79">
         <v>26</v>
       </c>
-      <c r="B135" s="16" t="s">
+      <c r="B135" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="C135" s="29"/>
-      <c r="D135" s="44"/>
-      <c r="E135" s="32"/>
-      <c r="F135" s="27">
+      <c r="C135" s="59"/>
+      <c r="D135" s="70"/>
+      <c r="E135" s="84"/>
+      <c r="F135" s="77">
         <v>0.69444444444444453</v>
       </c>
-      <c r="G135" s="14"/>
+      <c r="G135" s="78"/>
     </row>
     <row r="136" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="18"/>
-      <c r="B136" s="18"/>
-      <c r="C136" s="29"/>
-      <c r="D136" s="44"/>
-      <c r="E136" s="32"/>
-      <c r="F136" s="14"/>
-      <c r="G136" s="14"/>
+      <c r="A136" s="81"/>
+      <c r="B136" s="81"/>
+      <c r="C136" s="59"/>
+      <c r="D136" s="70"/>
+      <c r="E136" s="84"/>
+      <c r="F136" s="78"/>
+      <c r="G136" s="78"/>
     </row>
     <row r="137" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="16">
+      <c r="A137" s="79">
         <v>30</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C137" s="29"/>
-      <c r="D137" s="44"/>
-      <c r="E137" s="32"/>
-      <c r="F137" s="14"/>
-      <c r="G137" s="14"/>
+      <c r="C137" s="59"/>
+      <c r="D137" s="70"/>
+      <c r="E137" s="84"/>
+      <c r="F137" s="78"/>
+      <c r="G137" s="78"/>
     </row>
     <row r="138" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="17"/>
-      <c r="B138" s="17"/>
-      <c r="C138" s="29"/>
-      <c r="D138" s="44"/>
-      <c r="E138" s="32"/>
-      <c r="F138" s="14"/>
-      <c r="G138" s="14"/>
+      <c r="A138" s="80"/>
+      <c r="B138" s="80"/>
+      <c r="C138" s="59"/>
+      <c r="D138" s="70"/>
+      <c r="E138" s="84"/>
+      <c r="F138" s="78"/>
+      <c r="G138" s="78"/>
     </row>
     <row r="139" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="18"/>
-      <c r="B139" s="18"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="45"/>
-      <c r="E139" s="33"/>
-      <c r="F139" s="14"/>
-      <c r="G139" s="15"/>
+      <c r="A139" s="81"/>
+      <c r="B139" s="81"/>
+      <c r="C139" s="60"/>
+      <c r="D139" s="71"/>
+      <c r="E139" s="85"/>
+      <c r="F139" s="78"/>
+      <c r="G139" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="161">
-    <mergeCell ref="A1:G4"/>
-    <mergeCell ref="H1:H6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H14"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="H15:H18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="D9:D18"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="E15:E18"/>
-    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="F120:F124"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="B132:B134"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="F135:F139"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C139"/>
+    <mergeCell ref="E125:E139"/>
+    <mergeCell ref="F125:F129"/>
+    <mergeCell ref="G110:G114"/>
+    <mergeCell ref="A112:A114"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="A115:A117"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="C115:C124"/>
+    <mergeCell ref="D115:D139"/>
+    <mergeCell ref="E115:E124"/>
+    <mergeCell ref="F115:F119"/>
+    <mergeCell ref="G115:G124"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="C110:C114"/>
+    <mergeCell ref="D110:D114"/>
+    <mergeCell ref="E110:E114"/>
+    <mergeCell ref="F110:F114"/>
+    <mergeCell ref="F130:F134"/>
+    <mergeCell ref="A132:A134"/>
+    <mergeCell ref="G125:G139"/>
+    <mergeCell ref="A127:A129"/>
+    <mergeCell ref="B127:B129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A104:G107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="E86:E100"/>
+    <mergeCell ref="F86:F90"/>
+    <mergeCell ref="A88:A90"/>
+    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="F91:F95"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="F76:F80"/>
+    <mergeCell ref="G76:G100"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="F81:F85"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="F96:F100"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="C76:C85"/>
+    <mergeCell ref="D76:D100"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C100"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="E76:E85"/>
+    <mergeCell ref="A65:G68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="E71:E75"/>
+    <mergeCell ref="F71:F75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="I41:I49"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="I50:I59"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="F55:F59"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="G45:G54"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="C50:C59"/>
+    <mergeCell ref="F50:F54"/>
     <mergeCell ref="A24:G27"/>
     <mergeCell ref="H24:I29"/>
     <mergeCell ref="A28:A29"/>
@@ -3606,115 +3709,34 @@
     <mergeCell ref="B41:B42"/>
     <mergeCell ref="C41:C49"/>
     <mergeCell ref="H41:H59"/>
-    <mergeCell ref="I41:I49"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="I50:I59"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="G45:G54"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="C50:C59"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="A65:G68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
-    <mergeCell ref="E71:E75"/>
-    <mergeCell ref="F71:F75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="F76:F80"/>
-    <mergeCell ref="G76:G100"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="F81:F85"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="B83:B85"/>
-    <mergeCell ref="F96:F100"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="C76:C85"/>
-    <mergeCell ref="D76:D100"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C100"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="E76:E85"/>
-    <mergeCell ref="A104:G107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="E86:E100"/>
-    <mergeCell ref="F86:F90"/>
-    <mergeCell ref="A88:A90"/>
-    <mergeCell ref="B88:B90"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="F91:F95"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="G110:G114"/>
-    <mergeCell ref="A112:A114"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="A115:A117"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="C115:C124"/>
-    <mergeCell ref="D115:D139"/>
-    <mergeCell ref="E115:E124"/>
-    <mergeCell ref="F115:F119"/>
-    <mergeCell ref="G115:G124"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="C110:C114"/>
-    <mergeCell ref="D110:D114"/>
-    <mergeCell ref="E110:E114"/>
-    <mergeCell ref="F110:F114"/>
-    <mergeCell ref="F130:F134"/>
-    <mergeCell ref="A132:A134"/>
-    <mergeCell ref="G125:G139"/>
-    <mergeCell ref="A127:A129"/>
-    <mergeCell ref="B127:B129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B132:B134"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="F135:F139"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C139"/>
-    <mergeCell ref="E125:E139"/>
-    <mergeCell ref="F125:F129"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="F120:F124"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="H15:H18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="D9:D18"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="E15:E18"/>
+    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="A1:G4"/>
+    <mergeCell ref="H1:H6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H14"/>
+    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="1.75" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="27" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -3727,7 +3749,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.33203125" customWidth="1"/>
@@ -3735,360 +3757,341 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="76"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="76"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="76"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:8" ht="100.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="76"/>
-    </row>
-    <row r="5" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:8" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="76"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="76"/>
+        <v>5</v>
+      </c>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="17">
+        <v>0.24305555555555555</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="18">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="F6" s="17">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="49">
-        <v>0.24305555555555555</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="40">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="F7" s="49">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="G7" s="40">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="H7" s="92"/>
+        <v>9</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="92"/>
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="28">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="28">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F8" s="28">
+        <v>0.8125</v>
+      </c>
+      <c r="G8" s="27">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="42">
-        <v>0.24652777777777779</v>
-      </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="42">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F9" s="42">
-        <v>0.8125</v>
-      </c>
-      <c r="G9" s="67">
-        <v>0.87152777777777779</v>
-      </c>
-      <c r="H9" s="92"/>
+        <v>7</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="92"/>
+      <c r="A10" s="3">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="30">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="F10" s="30">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="G10" s="30">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="81">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="82">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="F11" s="82">
-        <v>0.80902777777777779</v>
-      </c>
-      <c r="G11" s="82">
-        <v>0.86458333333333337</v>
-      </c>
-      <c r="H11" s="92"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>15</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="92"/>
+      <c r="A12" s="6">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="25">
+        <v>0.25347222222222221</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="26">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="F12" s="26">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G12" s="26">
+        <v>0.85763888888888884</v>
+      </c>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="80">
-        <v>0.25347222222222221</v>
-      </c>
-      <c r="D13" s="80" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="57">
-        <v>0.69097222222222221</v>
-      </c>
-      <c r="F13" s="57">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="G13" s="57">
-        <v>0.85763888888888884</v>
-      </c>
-      <c r="H13" s="92"/>
+        <v>18</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="19"/>
     </row>
     <row r="14" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>20</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="92"/>
+      <c r="A14" s="13">
+        <v>21</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="28">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="D14" s="25"/>
+      <c r="E14" s="27">
+        <v>0.6875</v>
+      </c>
+      <c r="F14" s="27">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="G14" s="27">
+        <v>0.85069444444444442</v>
+      </c>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
-        <v>21</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="42">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="67">
-        <v>0.6875</v>
-      </c>
-      <c r="F15" s="67">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="G15" s="67">
-        <v>0.85069444444444442</v>
-      </c>
-      <c r="H15" s="76"/>
+      <c r="A15" s="4">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>25</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="76"/>
+      <c r="A16" s="5">
+        <v>26</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="17">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="18">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="F16" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0.84722222222222221</v>
+      </c>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="49">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="40">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="F17" s="40">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G17" s="40">
-        <v>0.84722222222222221</v>
-      </c>
-      <c r="H17" s="76"/>
-    </row>
-    <row r="18" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>30</v>
-      </c>
-      <c r="B18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="76"/>
-    </row>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="1.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="1.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="130.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="33.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="130.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="33.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="73" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="2.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="2.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="78" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4113,14 +4116,14 @@
     <row r="97" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="98" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="93.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="93.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="112" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="116" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="117" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4145,42 +4148,39 @@
     <row r="136" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="137" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="138" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="31">
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="A1:G4"/>
-    <mergeCell ref="H1:H6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H14"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D12"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="H15:H18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H1:H5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H13"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D11"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <pageMargins left="1.75" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="27" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -4192,402 +4192,378 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="76"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="76"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="76"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="15"/>
     </row>
     <row r="4" spans="1:13" ht="104.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="76"/>
-    </row>
-    <row r="5" spans="1:13" ht="58.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="124" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="53"/>
-      <c r="G5" s="124" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="53"/>
-      <c r="I5" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="53"/>
-      <c r="K5" s="124" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="53"/>
-      <c r="M5" s="76"/>
-    </row>
-    <row r="6" spans="1:13" ht="22.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="125" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="125"/>
-      <c r="I6" s="125" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125" t="s">
-        <v>6</v>
-      </c>
-      <c r="L6" s="125"/>
-      <c r="M6" s="76"/>
+      <c r="C5" s="125" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="126"/>
+      <c r="E5" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="95" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="16"/>
+      <c r="K5" s="95" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="16"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>1</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="97">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="D6" s="98"/>
+      <c r="E6" s="101" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="101"/>
+      <c r="G6" s="102">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H6" s="103"/>
+      <c r="I6" s="101">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="J6" s="101"/>
+      <c r="K6" s="106">
+        <v>0.84027777777777779</v>
+      </c>
+      <c r="L6" s="106"/>
+      <c r="M6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="115">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="D7" s="116"/>
-      <c r="E7" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="119">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H7" s="120"/>
-      <c r="I7" s="96">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="J7" s="96"/>
-      <c r="K7" s="123">
-        <v>0.84027777777777779</v>
-      </c>
-      <c r="L7" s="123"/>
-      <c r="M7" s="92"/>
+        <v>10</v>
+      </c>
+      <c r="C7" s="99"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="19"/>
     </row>
     <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>5</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="117"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="92"/>
+      <c r="A8" s="8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="99"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="108">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="H8" s="109"/>
+      <c r="I8" s="112">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="J8" s="112"/>
+      <c r="K8" s="96">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L8" s="96"/>
+      <c r="M8" s="19"/>
     </row>
     <row r="9" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="99"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="19"/>
+    </row>
+    <row r="10" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
         <v>11</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="97">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="H9" s="98"/>
-      <c r="I9" s="101">
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="J9" s="101"/>
-      <c r="K9" s="102">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L9" s="102"/>
-      <c r="M9" s="92"/>
-    </row>
-    <row r="10" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <v>10</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="101"/>
-      <c r="J10" s="101"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="92"/>
+      <c r="B10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="99"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="119">
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="H10" s="120"/>
+      <c r="I10" s="123">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="J10" s="123"/>
+      <c r="K10" s="124">
+        <v>0.82986111111111116</v>
+      </c>
+      <c r="L10" s="124"/>
+      <c r="M10" s="19"/>
     </row>
     <row r="11" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="117"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="109">
-        <v>0.67013888888888884</v>
-      </c>
-      <c r="H11" s="110"/>
-      <c r="I11" s="113">
-        <v>0.77430555555555558</v>
-      </c>
-      <c r="J11" s="113"/>
-      <c r="K11" s="114">
-        <v>0.82986111111111116</v>
-      </c>
-      <c r="L11" s="114"/>
-      <c r="M11" s="92"/>
+        <v>7</v>
+      </c>
+      <c r="C11" s="99"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>15</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="114"/>
-      <c r="M12" s="92"/>
+      <c r="A12" s="9">
+        <v>16</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="99"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="113">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H12" s="114"/>
+      <c r="I12" s="117">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="J12" s="117"/>
+      <c r="K12" s="118">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="L12" s="118"/>
+      <c r="M12" s="19"/>
     </row>
     <row r="13" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="103">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H13" s="104"/>
-      <c r="I13" s="107">
-        <v>0.76736111111111116</v>
-      </c>
-      <c r="J13" s="107"/>
-      <c r="K13" s="108">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="L13" s="108"/>
-      <c r="M13" s="92"/>
+        <v>11</v>
+      </c>
+      <c r="C13" s="99"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="19"/>
     </row>
     <row r="14" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
-        <v>20</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="92"/>
+      <c r="A14" s="7">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="99"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="107">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="H14" s="107"/>
+      <c r="I14" s="101">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="J14" s="101"/>
+      <c r="K14" s="107">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="L14" s="107"/>
+      <c r="M14" s="15"/>
     </row>
     <row r="15" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="95">
-        <v>0.66319444444444442</v>
-      </c>
-      <c r="H15" s="95"/>
-      <c r="I15" s="96">
-        <v>0.76388888888888884</v>
-      </c>
-      <c r="J15" s="96"/>
-      <c r="K15" s="95">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="L15" s="95"/>
-      <c r="M15" s="76"/>
+        <v>18</v>
+      </c>
+      <c r="C15" s="99"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="101"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>25</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="76"/>
+      <c r="A16" s="8">
+        <v>26</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="99"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="96">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="H16" s="96"/>
+      <c r="I16" s="112">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="J16" s="112"/>
+      <c r="K16" s="96">
+        <v>0.8125</v>
+      </c>
+      <c r="L16" s="96"/>
+      <c r="M16" s="15"/>
     </row>
     <row r="17" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="102">
-        <v>0.65972222222222221</v>
-      </c>
-      <c r="H17" s="102"/>
-      <c r="I17" s="101">
-        <v>0.75694444444444442</v>
-      </c>
-      <c r="J17" s="101"/>
-      <c r="K17" s="102">
-        <v>0.8125</v>
-      </c>
-      <c r="L17" s="102"/>
-      <c r="M17" s="76"/>
-    </row>
-    <row r="18" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
-        <v>31</v>
-      </c>
-      <c r="B18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="101"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="76"/>
-    </row>
-    <row r="23" spans="1:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:13" ht="52.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:13" ht="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="15"/>
+    </row>
+    <row r="22" spans="1:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:13" ht="52.2" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:13" ht="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4617,45 +4593,37 @@
     <row r="55" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="29">
+    <mergeCell ref="M6:M13"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="I8:J9"/>
+    <mergeCell ref="K8:L9"/>
+    <mergeCell ref="M14:M17"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="G10:H11"/>
+    <mergeCell ref="I10:J11"/>
+    <mergeCell ref="K10:L11"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="C6:D17"/>
+    <mergeCell ref="E6:F17"/>
+    <mergeCell ref="G6:H7"/>
+    <mergeCell ref="I6:J7"/>
+    <mergeCell ref="K6:L7"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
     <mergeCell ref="A1:L4"/>
-    <mergeCell ref="M1:M6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="M1:M5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K17:L18"/>
-    <mergeCell ref="C7:D18"/>
-    <mergeCell ref="E7:F18"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="I15:J16"/>
-    <mergeCell ref="K15:L16"/>
-    <mergeCell ref="M7:M14"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="M15:M18"/>
-    <mergeCell ref="G13:H14"/>
-    <mergeCell ref="I13:J14"/>
-    <mergeCell ref="K13:L14"/>
-    <mergeCell ref="G11:H12"/>
-    <mergeCell ref="I11:J12"/>
-    <mergeCell ref="K11:L12"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="I17:J18"/>
   </mergeCells>
   <pageMargins left="1.75" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="57" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
